--- a/docs/Logic Requirements/Ageipelago Montezuma.xlsx
+++ b/docs/Logic Requirements/Ageipelago Montezuma.xlsx
@@ -5,15 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/BB6DD295C338E39F/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{52ABE43D-D0EC-4445-926D-BAE51B3B6EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158F2B9D-FCA6-4A28-82F9-DCABEFC9D2B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A599EB4-0E69-49C9-9AFB-167A96F4B5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28545" yWindow="1335" windowWidth="27045" windowHeight="13740" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{17AA2DA1-B674-46E5-8909-131BC3A5F213}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Montezuma" sheetId="1" r:id="rId1"/>
+    <sheet name="Reign of Blood" sheetId="2" r:id="rId2"/>
+    <sheet name="The Triple Alliance" sheetId="3" r:id="rId3"/>
+    <sheet name="Quetzalcoatl" sheetId="4" r:id="rId4"/>
+    <sheet name="La Noche Triste" sheetId="5" r:id="rId5"/>
+    <sheet name="The Boiling Lake" sheetId="6" r:id="rId6"/>
+    <sheet name="Broken Spears" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="180">
   <si>
     <t>Scenario</t>
   </si>
@@ -1313,84 +1319,6 @@
 To collect the Relic, the Player must have unlocked the Monastery and Monks.</t>
   </si>
   <si>
-    <t>To Rrach the Elite Cannon Galleons, the Player must have unlocked any Ship.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-12 Eagle Warriors
-12 Long Swordsmen (Feudal Age)
-4 Long Swordsmen (Castle Age)
-1 Battering Ram
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-No Castle Age
-12 Men-at-Arms
-1 Battering Ram
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2365,95 +2293,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-3 Fast Fire Ships
-6 Galleons
-2 Elite Cannon Galleons
-8 Halbardiers
-6 Elite Conquistadores
-1 Missionary
-2 Trebuchets
-2 Siege Rams
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3 Fast Fire Ships
-6 Galleons
-2 Elite Cannon Galleons
-6 Elite Conquistadores
-2 Trebuchets
-2 Siege Rams
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3 Fast Fire Ships
-6 Galleons
-2 Elite Cannon Galleons
-8 Halbardiers
-6 Elite Conquistadores
-2 Missionaries
-2 Trebuchets
-2 Siege Rams</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
 12 Paladins
 10 Elite Conquistadores
 2 Onagers
@@ -2538,6 +2377,700 @@
     </r>
   </si>
   <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Militia</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Galley</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Wild Turkey</t>
+  </si>
+  <si>
+    <t>Javelina</t>
+  </si>
+  <si>
+    <t>Jaguar</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+12 Eagle Warriors
+12 Men-at-Arms (Feudal Age)
+4 Long Swordsmen (Castle Age)
+1 Battering Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+No Castle Age
+12 Men-at-Arms
+1 Battering Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eagle Warrior
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Eagle Scout</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Plumed Archer</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Skirmisher
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Plumed Archer
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Son of Ornlu</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <t>Eagle Warrior</t>
+  </si>
+  <si>
+    <t>Jaguar Warrior</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mangonel
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fish Trap</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Petard</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eagle Scout
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Eagle Warrior
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Eagle Warrior
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Skirmisher
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Skirmisher
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Crossbowman
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Arbalester
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Conquistador</t>
+  </si>
+  <si>
+    <t>Elite Conquistdor</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Missionary
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cavalier
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Bombard Tower</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Ornlu the Wolf</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Missionary</t>
+  </si>
+  <si>
+    <t>Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Demolition Ship</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Requires Boats</t>
+  </si>
+  <si>
+    <t>Elite Jaguar Warrior</t>
+  </si>
+  <si>
+    <t>Arbalesters</t>
+  </si>
+  <si>
+    <t>Elite Eagle Warrior</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Elite Conquistador</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">War Galley
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Galleon
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>To Reach the Elite Cannon Galleons, the Player must have unlocked any Ship.</t>
+  </si>
+  <si>
+    <t>Fast Fire Ship</t>
+  </si>
+  <si>
+    <t>Carrack</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 Fast Fire Ships
+4 Galleons
+3 Carracks
+2 Elite Cannon Galleons
+8 Halberdiers
+6 Elite Conquistadores
+1 Missionary
+2 Trebuchets
+2 Siege Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 Fast Fire Ships
+4 Galleons
+3 Carracks
+2 Elite Cannon Galleons
+6 Elite Conquistadores
+2 Trebuchets
+2 Siege Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 Fast Fire Ships
+4 Galleons
+3 Carracks
+2 Elite Cannon Galleons
+8 Halbardiers
+6 Elite Conquistadores
+2 Missionaries
+2 Trebuchets
+2 Siege Rams</t>
+    </r>
+  </si>
+  <si>
+    <t>Siege Ram</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Halberdier
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Paladin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bombard Cannon
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2559,7 +3092,7 @@
       </rPr>
       <t xml:space="preserve">
 Starting Units:
-14 Elite Eagle Warriors
+14 Eagle Scouts
 Later:
 10 Elite Eagle Warriors
 10 Elite Jaguar Warriors
@@ -2588,7 +3121,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Starting Units:
-14 Elite Eagle Warriors
+14 Eagle Scouts
 Later:
 5 Elite Eagle Warriors
 1 Siege Ram
@@ -2616,13 +3149,44 @@
       <t xml:space="preserve">
 Identical to Standard</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Jaguar Warrior
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Scorpion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Requires Transport Ship</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2748,6 +3312,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2757,7 +3326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2845,11 +3414,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2885,6 +3502,69 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3276,13 +3956,13 @@
       <c r="H4" s="7"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -3318,13 +3998,13 @@
         <v>49</v>
       </c>
       <c r="J5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -3358,13 +4038,13 @@
         <v>23</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
@@ -3400,13 +4080,13 @@
         <v>53</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
@@ -3440,10 +4120,10 @@
         <v>31</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -3475,27 +4155,2575 @@
         <v>57</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AB02A6-6705-462C-AFB4-F8F81317FF41}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D318CCD2-3435-443A-AA52-8195CCD9461A}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484DAF4A-DAC4-4168-AC16-D57BBA4F7C96}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE449FBF-0F17-4D22-AA89-F09A1B96E52D}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5D7B81-02BA-4052-9F47-725EAD681E49}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5207D59-AEA2-42AF-9AD1-593F3FB5CDAE}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G10" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G20" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>